--- a/marketing_forms/011_download_budget_wedding_ideas--marketing_forms.xlsx
+++ b/marketing_forms/011_download_budget_wedding_ideas--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Download Budget Wedding Ideas Form</t>
+          <t>Form Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_budget_category</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Budget Category</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Event Description</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_contact_email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_contact_phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Contact Phone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_contact_email</t>
+          <t>form_planning_info_decorations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Planning Info - Decorations</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_contact_email</t>
+          <t>form_planning_info_music</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Planning Info - Music</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_contact_phone</t>
+          <t>form_planning_info_food_beverages</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Planning Info - Food &amp; Beverages</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_planning_info</t>
+          <t>form_follow_up</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Planning Info</t>
+          <t>Follow-up</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_planning_info</t>
+          <t>form_special_requests</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Planning Info</t>
+          <t>Special Requests</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_planning_info</t>
+          <t>form_venue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Planning Info</t>
+          <t>Venue</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,21 +768,90 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_follow_up</t>
+          <t>form_budget_estimate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Follow-up</t>
+          <t>Budget Estimate</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>form_guests</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Guests</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>form_dress_code</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dress Code</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>form_guest_count</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Estimated Guest Count</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -799,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,34 +896,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_budget_category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'marketing_forms'}</t>
+          <t>marketing_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing Forms'}</t>
+          <t>Marketing Forms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_budget_category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'wedding_forms'}</t>
+          <t>wedding_forms</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Wedding Forms'}</t>
+          <t>Wedding Forms</t>
         </is>
       </c>
     </row>
@@ -866,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -883,12 +952,114 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>form_venue_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>church</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Church</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>form_venue_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>outdoor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Outdoor</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>form_venue_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>form_dress_code_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>formal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>form_dress_code_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>casual</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Casual</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>form_dress_code_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
